--- a/Well_Template_PZero.xlsx
+++ b/Well_Template_PZero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bistek\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPOS\WellTemplate_PZero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C370FD-F37B-47AA-8BFB-C736F412E283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2CACAB-3962-479B-A766-9AD4DC5E7457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="28800" windowHeight="15370" xr2:uid="{B4582437-E486-4031-BCD8-A7320F9C17C9}"/>
+    <workbookView xWindow="3300" yWindow="3300" windowWidth="28800" windowHeight="15370" xr2:uid="{B4582437-E486-4031-BCD8-A7320F9C17C9}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="1" r:id="rId1"/>
@@ -360,7 +360,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
-            <a:t> Name of the weel</a:t>
+            <a:t> Name of the well</a:t>
           </a:r>
         </a:p>
         <a:p>
